--- a/Backlog.xlsx
+++ b/Backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\Loyalty\loyalty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96C9C16-ECAD-4F60-9CAE-9E6E5A5F9B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B697081A-1383-46FD-8F8B-E8863D6E0863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="26">
   <si>
     <t>Descripción</t>
   </si>
@@ -54,9 +54,6 @@
     <t>Tarjeta digital / mensajes: adaptar automáticamente el color del texto/mensaje según si el fondo configurado es oscuro o claro.</t>
   </si>
   <si>
-    <t>Tarjetas de regalo: enviar por Gmail.</t>
-  </si>
-  <si>
     <t>Danny</t>
   </si>
   <si>
@@ -97,6 +94,15 @@
   </si>
   <si>
     <t>Tarjetas de regalo: validar en STG el envío real por Resend, apertura del claim link, Wallet y reenvío con rotación del token.</t>
+  </si>
+  <si>
+    <t>Benjamin</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Tarjetas de regalo: enviar por mail.</t>
   </si>
 </sst>
 </file>
@@ -203,30 +209,6 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF1F2937"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -261,6 +243,30 @@
       </font>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF1F2937"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -275,12 +281,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8FB71062-6281-42C0-A54F-9C18896C9BFD}" name="Table1" displayName="Table1" ref="A1:C18" totalsRowShown="0" headerRowDxfId="2" dataDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8FB71062-6281-42C0-A54F-9C18896C9BFD}" name="Table1" displayName="Table1" ref="A1:C18" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <autoFilter ref="A1:C18" xr:uid="{8FB71062-6281-42C0-A54F-9C18896C9BFD}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E0DEC2B8-DF54-41BF-AF1E-74AD0C5FC7BA}" name="Descripción" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{E0DEC2B8-DF54-41BF-AF1E-74AD0C5FC7BA}" name="Descripción" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{220F81DC-914C-436B-B8D8-C468BE95FFD1}" name="Status" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{DE7A4243-DB60-4221-9442-67423B0CF4FF}" name="Asignado" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{DE7A4243-DB60-4221-9442-67423B0CF4FF}" name="Asignado" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -552,7 +558,7 @@
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="93.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="104.42578125" customWidth="1"/>
     <col min="2" max="2" width="20.140625" customWidth="1"/>
     <col min="3" max="3" width="25.140625" customWidth="1"/>
   </cols>
@@ -573,10 +579,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="28.5">
@@ -614,29 +620,29 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="28.5">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>4</v>
@@ -647,7 +653,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>4</v>
@@ -658,7 +664,7 @@
     </row>
     <row r="10" spans="1:3" ht="28.5">
       <c r="A10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>4</v>
@@ -669,18 +675,18 @@
     </row>
     <row r="11" spans="1:3" ht="28.5">
       <c r="A11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>4</v>
@@ -691,7 +697,7 @@
     </row>
     <row r="13" spans="1:3" ht="28.5">
       <c r="A13" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>4</v>
@@ -702,7 +708,7 @@
     </row>
     <row r="14" spans="1:3" ht="28.5">
       <c r="A14" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>4</v>
@@ -713,7 +719,7 @@
     </row>
     <row r="15" spans="1:3" ht="28.5">
       <c r="A15" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>4</v>
@@ -724,7 +730,7 @@
     </row>
     <row r="16" spans="1:3" ht="28.5">
       <c r="A16" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>4</v>
@@ -735,7 +741,7 @@
     </row>
     <row r="17" spans="1:3" ht="28.5">
       <c r="A17" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>4</v>
@@ -746,13 +752,13 @@
     </row>
     <row r="18" spans="1:3" ht="28.5">
       <c r="A18" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Backlog.xlsx
+++ b/Backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\Loyalty\loyalty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B697081A-1383-46FD-8F8B-E8863D6E0863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B70B80-864E-4CFB-B3F9-785E3C47BDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -170,7 +170,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="10">
     <dxf>
       <font>
         <b val="0"/>
@@ -188,6 +188,56 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -281,12 +331,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8FB71062-6281-42C0-A54F-9C18896C9BFD}" name="Table1" displayName="Table1" ref="A1:C18" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8FB71062-6281-42C0-A54F-9C18896C9BFD}" name="Table1" displayName="Table1" ref="A1:C18" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="A1:C18" xr:uid="{8FB71062-6281-42C0-A54F-9C18896C9BFD}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E0DEC2B8-DF54-41BF-AF1E-74AD0C5FC7BA}" name="Descripción" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{220F81DC-914C-436B-B8D8-C468BE95FFD1}" name="Status" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{DE7A4243-DB60-4221-9442-67423B0CF4FF}" name="Asignado" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{E0DEC2B8-DF54-41BF-AF1E-74AD0C5FC7BA}" name="Descripción" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{220F81DC-914C-436B-B8D8-C468BE95FFD1}" name="Status" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{DE7A4243-DB60-4221-9442-67423B0CF4FF}" name="Asignado" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -585,7 +635,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="28.5">
+    <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -678,7 +728,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>9</v>
@@ -706,15 +756,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="28.5">
+    <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="28.5">
@@ -762,6 +812,21 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B18">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+      <formula>"Done"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:C16">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+      <formula>"Done"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B18">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"En progreso"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <tableParts count="1">

--- a/Backlog.xlsx
+++ b/Backlog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27103"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\Loyalty\loyalty\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benji\source\repos\loyalty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B70B80-864E-4CFB-B3F9-785E3C47BDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3706A28D-8CD5-41BB-A7F0-9B0A3A4DACC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog" sheetId="1" r:id="rId1"/>
@@ -170,35 +170,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -221,23 +193,31 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -331,12 +311,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8FB71062-6281-42C0-A54F-9C18896C9BFD}" name="Table1" displayName="Table1" ref="A1:C18" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8FB71062-6281-42C0-A54F-9C18896C9BFD}" name="Table1" displayName="Table1" ref="A1:C18" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A1:C18" xr:uid="{8FB71062-6281-42C0-A54F-9C18896C9BFD}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E0DEC2B8-DF54-41BF-AF1E-74AD0C5FC7BA}" name="Descripción" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{220F81DC-914C-436B-B8D8-C468BE95FFD1}" name="Status" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{DE7A4243-DB60-4221-9442-67423B0CF4FF}" name="Asignado" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{E0DEC2B8-DF54-41BF-AF1E-74AD0C5FC7BA}" name="Descripción" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{220F81DC-914C-436B-B8D8-C468BE95FFD1}" name="Status" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{DE7A4243-DB60-4221-9442-67423B0CF4FF}" name="Asignado" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -606,11 +586,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="104.42578125" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" customWidth="1"/>
-    <col min="3" max="3" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="104.44140625" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" customWidth="1"/>
+    <col min="3" max="3" width="25.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -624,7 +604,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="28.5">
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -646,18 +626,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="28.5">
+    <row r="4" spans="1:3" ht="27.6">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="28.5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="27.6">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -690,15 +670,15 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="28.5">
+    <row r="8" spans="1:3" ht="27.6">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -706,24 +686,24 @@
         <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="28.5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="27.6">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="28.5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="27.6">
       <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
@@ -739,13 +719,13 @@
         <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="28.5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="27.6">
       <c r="A13" s="2" t="s">
         <v>17</v>
       </c>
@@ -767,7 +747,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="28.5">
+    <row r="15" spans="1:3" ht="27.6">
       <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
@@ -778,7 +758,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="28.5">
+    <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
         <v>20</v>
       </c>
@@ -789,7 +769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="28.5">
+    <row r="17" spans="1:3" ht="27.6">
       <c r="A17" s="2" t="s">
         <v>21</v>
       </c>
@@ -800,7 +780,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="28.5">
+    <row r="18" spans="1:3" ht="27.6">
       <c r="A18" s="2" t="s">
         <v>22</v>
       </c>
@@ -813,18 +793,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B18">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"En progreso"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C16">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"Done"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B18">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>"En progreso"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Backlog.xlsx
+++ b/Backlog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27103"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benji\source\repos\loyalty\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\Loyalty\loyalty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3706A28D-8CD5-41BB-A7F0-9B0A3A4DACC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64ACAA4F-78C5-415E-B625-CA9A2EC7E7B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="25">
   <si>
     <t>Descripción</t>
   </si>
@@ -70,9 +70,6 @@
   </si>
   <si>
     <t>Diseño y configuración: reorganizar en tabs Tarjeta digital / Tarjetas de regalo / Puntos y beneficios y mover la configuración de Tarjetas de regalo al tab correspondiente.</t>
-  </si>
-  <si>
-    <t>En progreso</t>
   </si>
   <si>
     <t>Tarjetas de regalo: corregir que no se pueden seleccionar los montos predefinidos.</t>
@@ -170,7 +167,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="9">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -178,26 +175,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -297,6 +274,36 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -311,12 +318,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8FB71062-6281-42C0-A54F-9C18896C9BFD}" name="Table1" displayName="Table1" ref="A1:C18" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8FB71062-6281-42C0-A54F-9C18896C9BFD}" name="Table1" displayName="Table1" ref="A1:C18" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="A1:C18" xr:uid="{8FB71062-6281-42C0-A54F-9C18896C9BFD}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E0DEC2B8-DF54-41BF-AF1E-74AD0C5FC7BA}" name="Descripción" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{220F81DC-914C-436B-B8D8-C468BE95FFD1}" name="Status" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{DE7A4243-DB60-4221-9442-67423B0CF4FF}" name="Asignado" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{E0DEC2B8-DF54-41BF-AF1E-74AD0C5FC7BA}" name="Descripción" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{220F81DC-914C-436B-B8D8-C468BE95FFD1}" name="Status" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{DE7A4243-DB60-4221-9442-67423B0CF4FF}" name="Asignado" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -586,11 +593,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="104.44140625" customWidth="1"/>
-    <col min="2" max="2" width="20.109375" customWidth="1"/>
-    <col min="3" max="3" width="25.109375" customWidth="1"/>
+    <col min="1" max="1" width="104.42578125" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" customWidth="1"/>
+    <col min="3" max="3" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -604,15 +611,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" ht="28.5">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -626,34 +633,34 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="27.6">
+    <row r="4" spans="1:3" ht="28.5">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="27.6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="28.5">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>9</v>
@@ -664,21 +671,21 @@
         <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="27.6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="28.5">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -686,29 +693,29 @@
         <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="27.6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="28.5">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="27.6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="28.5">
       <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>9</v>
@@ -716,40 +723,40 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="28.5">
+      <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="27.6">
-      <c r="A13" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="B13" s="2" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="27.6">
+    <row r="15" spans="1:3" ht="28.5">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>4</v>
@@ -758,9 +765,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" ht="28.5">
       <c r="A16" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>4</v>
@@ -769,9 +776,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="27.6">
+    <row r="17" spans="1:3" ht="28.5">
       <c r="A17" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>4</v>
@@ -780,12 +787,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="27.6">
+    <row r="18" spans="1:3" ht="28.5">
       <c r="A18" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>9</v>
@@ -793,15 +800,20 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B18">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"En progreso"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C16">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+      <formula>"Done"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Backlog.xlsx
+++ b/Backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\Loyalty\loyalty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64ACAA4F-78C5-415E-B625-CA9A2EC7E7B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90BDC540-CDAE-4200-8CC4-06879C0D2743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="26">
   <si>
     <t>Descripción</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>Tarjetas de regalo: enviar por mail.</t>
+  </si>
+  <si>
+    <t>Revisar correo de Gift Card no se vaya al junk</t>
   </si>
 </sst>
 </file>
@@ -167,7 +170,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="11">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -175,6 +178,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -273,6 +286,16 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -318,12 +341,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8FB71062-6281-42C0-A54F-9C18896C9BFD}" name="Table1" displayName="Table1" ref="A1:C18" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
-  <autoFilter ref="A1:C18" xr:uid="{8FB71062-6281-42C0-A54F-9C18896C9BFD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8FB71062-6281-42C0-A54F-9C18896C9BFD}" name="Table1" displayName="Table1" ref="A1:C19" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:C19" xr:uid="{8FB71062-6281-42C0-A54F-9C18896C9BFD}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E0DEC2B8-DF54-41BF-AF1E-74AD0C5FC7BA}" name="Descripción" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{220F81DC-914C-436B-B8D8-C468BE95FFD1}" name="Status" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{DE7A4243-DB60-4221-9442-67423B0CF4FF}" name="Asignado" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{E0DEC2B8-DF54-41BF-AF1E-74AD0C5FC7BA}" name="Descripción" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{220F81DC-914C-436B-B8D8-C468BE95FFD1}" name="Status" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{DE7A4243-DB60-4221-9442-67423B0CF4FF}" name="Asignado" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -592,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="104.42578125" customWidth="1"/>
@@ -798,22 +821,31 @@
         <v>9</v>
       </c>
     </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="2"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B18">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+  <conditionalFormatting sqref="B2:B19">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"En progreso"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C16">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Backlog.xlsx
+++ b/Backlog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\Loyalty\loyalty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90BDC540-CDAE-4200-8CC4-06879C0D2743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CC64EE-A8B5-43C9-BD94-41DA86BA54CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog" sheetId="1" r:id="rId1"/>
@@ -81,12 +81,6 @@
     <t>Mensajes: rediseñar el flujo de envío; reducir confirmaciones repetidas y corregir/mejorar el preview.</t>
   </si>
   <si>
-    <t>Google Wallet: agregar una imagen/foto de branding usando el asset y ubicación nativos más adecuados para Google Wallet.</t>
-  </si>
-  <si>
-    <t>Google Wallet: asegurar que el color de la tarjeta se actualice/refresque cuando cambia el branding del tenant.</t>
-  </si>
-  <si>
     <t>Email transaccional: actualizar la UI/configuración de proveedor para reflejar Resend en lugar de mostrar únicamente Cloudflare.</t>
   </si>
   <si>
@@ -103,6 +97,12 @@
   </si>
   <si>
     <t>Revisar correo de Gift Card no se vaya al junk</t>
+  </si>
+  <si>
+    <t>Loyalty Google Wallet: agregar una imagen/foto de branding usando el asset y ubicación nativos más adecuados para Google Wallet.</t>
+  </si>
+  <si>
+    <t>Loyalty Google Wallet: asegurar que el color de la tarjeta se actualice/refresque cuando cambia el branding del tenant.</t>
   </si>
 </sst>
 </file>
@@ -170,27 +170,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="9">
     <dxf>
       <font>
         <b val="0"/>
@@ -341,12 +321,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8FB71062-6281-42C0-A54F-9C18896C9BFD}" name="Table1" displayName="Table1" ref="A1:C19" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8FB71062-6281-42C0-A54F-9C18896C9BFD}" name="Table1" displayName="Table1" ref="A1:C19" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <autoFilter ref="A1:C19" xr:uid="{8FB71062-6281-42C0-A54F-9C18896C9BFD}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E0DEC2B8-DF54-41BF-AF1E-74AD0C5FC7BA}" name="Descripción" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{220F81DC-914C-436B-B8D8-C468BE95FFD1}" name="Status" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{DE7A4243-DB60-4221-9442-67423B0CF4FF}" name="Asignado" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{E0DEC2B8-DF54-41BF-AF1E-74AD0C5FC7BA}" name="Descripción" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{220F81DC-914C-436B-B8D8-C468BE95FFD1}" name="Status" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{DE7A4243-DB60-4221-9442-67423B0CF4FF}" name="Asignado" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -639,10 +619,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -661,10 +641,10 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="28.5">
@@ -672,7 +652,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
@@ -680,10 +660,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>9</v>
@@ -694,10 +674,10 @@
         <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="28.5">
@@ -705,10 +685,10 @@
         <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -716,10 +696,10 @@
         <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="28.5">
@@ -727,10 +707,10 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="28.5">
@@ -738,7 +718,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>9</v>
@@ -749,10 +729,10 @@
         <v>15</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="28.5">
@@ -760,7 +740,7 @@
         <v>16</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>9</v>
@@ -771,7 +751,7 @@
         <v>17</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>9</v>
@@ -779,7 +759,7 @@
     </row>
     <row r="15" spans="1:3" ht="28.5">
       <c r="A15" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>4</v>
@@ -790,7 +770,7 @@
     </row>
     <row r="16" spans="1:3" ht="28.5">
       <c r="A16" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>4</v>
@@ -801,7 +781,7 @@
     </row>
     <row r="17" spans="1:3" ht="28.5">
       <c r="A17" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>4</v>
@@ -812,10 +792,10 @@
     </row>
     <row r="18" spans="1:3" ht="28.5">
       <c r="A18" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>9</v>
@@ -823,7 +803,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>4</v>
@@ -832,20 +812,20 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B19">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"En progreso"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C16">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
